--- a/output/roomself_excel/3735.xlsx
+++ b/output/roomself_excel/3735.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>328135</v>
+        <v>144072</v>
       </c>
       <c r="D2" t="n">
-        <v>5056</v>
+        <v>3236</v>
       </c>
       <c r="E2" t="n">
-        <v>945</v>
+        <v>403</v>
       </c>
       <c r="F2" t="n">
-        <v>411</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73075</v>
+        <v>208435</v>
       </c>
       <c r="D3" t="n">
-        <v>2320</v>
+        <v>3816</v>
       </c>
       <c r="E3" t="n">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="F3" t="n">
-        <v>206</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>443647</v>
+        <v>83583</v>
       </c>
       <c r="D4" t="n">
-        <v>8272</v>
+        <v>2336</v>
       </c>
       <c r="E4" t="n">
-        <v>923</v>
+        <v>251</v>
       </c>
       <c r="F4" t="n">
-        <v>838</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83583</v>
+        <v>127116</v>
       </c>
       <c r="D5" t="n">
-        <v>2336</v>
+        <v>2900</v>
       </c>
       <c r="E5" t="n">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="F5" t="n">
         <v>21</v>
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>127116</v>
+        <v>98438</v>
       </c>
       <c r="D6" t="n">
-        <v>2900</v>
+        <v>2620</v>
       </c>
       <c r="E6" t="n">
-        <v>297</v>
+        <v>376</v>
       </c>
       <c r="F6" t="n">
-        <v>165</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18189</v>
+        <v>91140</v>
       </c>
       <c r="D8" t="n">
-        <v>1080</v>
+        <v>2476</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18576</v>
+        <v>103295</v>
       </c>
       <c r="D9" t="n">
-        <v>1092</v>
+        <v>2592</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>98438</v>
+        <v>18576</v>
       </c>
       <c r="D10" t="n">
-        <v>2620</v>
+        <v>1092</v>
       </c>
       <c r="E10" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33300</v>
+        <v>224840</v>
       </c>
       <c r="D11" t="n">
-        <v>1460</v>
+        <v>3924</v>
       </c>
       <c r="E11" t="n">
-        <v>206</v>
+        <v>639</v>
       </c>
       <c r="F11" t="n">
-        <v>201</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12">
@@ -690,15 +690,81 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>73075</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E12" t="n">
+        <v>416</v>
+      </c>
+      <c r="F12" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>18189</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>33300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E14" t="n">
+        <v>206</v>
+      </c>
+      <c r="F14" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>29946</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D15" t="n">
         <v>1388</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E15" t="n">
         <v>186</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F15" t="n">
         <v>21</v>
       </c>
     </row>

--- a/output/roomself_excel/3735.xlsx
+++ b/output/roomself_excel/3735.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3236</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>403</v>
       </c>
-      <c r="F2" t="n">
-        <v>21</v>
-      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>3816</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>410</v>
       </c>
-      <c r="F3" t="n">
-        <v>21</v>
-      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +555,20 @@
       <c r="D4" t="n">
         <v>2336</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>251</v>
       </c>
-      <c r="F4" t="n">
-        <v>21</v>
-      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +585,20 @@
       <c r="D5" t="n">
         <v>2900</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>295</v>
       </c>
-      <c r="F5" t="n">
-        <v>21</v>
-      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +615,27 @@
       <c r="D6" t="n">
         <v>2620</v>
       </c>
-      <c r="E6" t="n">
-        <v>376</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>122</v>
+        <v>101</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>355</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +653,20 @@
       <c r="D7" t="n">
         <v>1868</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>282</v>
       </c>
-      <c r="F7" t="n">
-        <v>21</v>
-      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +683,12 @@
       <c r="D8" t="n">
         <v>2476</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +705,27 @@
       <c r="D9" t="n">
         <v>2592</v>
       </c>
-      <c r="E9" t="n">
-        <v>411</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>306</v>
+        <v>365</v>
+      </c>
+      <c r="G9" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>404</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +743,12 @@
       <c r="D10" t="n">
         <v>1092</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +765,27 @@
       <c r="D11" t="n">
         <v>3924</v>
       </c>
-      <c r="E11" t="n">
-        <v>639</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>388</v>
+        <v>616</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>365</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +803,27 @@
       <c r="D12" t="n">
         <v>2320</v>
       </c>
-      <c r="E12" t="n">
-        <v>416</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>206</v>
+        <v>185</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>395</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +841,12 @@
       <c r="D13" t="n">
         <v>1080</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +863,27 @@
       <c r="D14" t="n">
         <v>1460</v>
       </c>
-      <c r="E14" t="n">
-        <v>206</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>201</v>
+        <v>180</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>185</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +901,20 @@
       <c r="D15" t="n">
         <v>1388</v>
       </c>
-      <c r="E15" t="n">
-        <v>186</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
